--- a/Dataset/Data_CFR.xlsx
+++ b/Dataset/Data_CFR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Power BI 30 Days\Practice File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prateek\Desktop\Repos\restaurant-analysis-powerbi\Dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C060F03-8E53-43D9-8242-1AD0D085FB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAF9C62-7682-44A8-BC3E-C9B44FDB90D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{D9EC1753-4A03-47A3-AA03-1AF5C4023F33}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="22920" windowHeight="13755" activeTab="1" xr2:uid="{D9EC1753-4A03-47A3-AA03-1AF5C4023F33}"/>
   </bookViews>
   <sheets>
     <sheet name="Food_Details" sheetId="3" r:id="rId1"/>
@@ -37,6 +37,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -291,7 +294,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -666,14 +669,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57C2090F-16F8-4AC8-B4E2-FD6164A576CC}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
@@ -684,7 +687,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>2142</v>
       </c>
@@ -695,7 +698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2152</v>
       </c>
@@ -706,7 +709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>2145</v>
       </c>
@@ -717,7 +720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>2149</v>
       </c>
@@ -728,7 +731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>2141</v>
       </c>
@@ -739,7 +742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>2147</v>
       </c>
@@ -750,7 +753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>2161</v>
       </c>
@@ -761,7 +764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>2148</v>
       </c>
@@ -772,7 +775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>2150</v>
       </c>
@@ -783,7 +786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>2144</v>
       </c>
@@ -794,7 +797,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>2165</v>
       </c>
@@ -805,7 +808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>2163</v>
       </c>
@@ -816,7 +819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>2143</v>
       </c>
@@ -827,7 +830,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>2155</v>
       </c>
@@ -838,7 +841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>2154</v>
       </c>
@@ -849,7 +852,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>2164</v>
       </c>
@@ -860,7 +863,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>2166</v>
       </c>
@@ -871,7 +874,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>2160</v>
       </c>
@@ -882,7 +885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>2167</v>
       </c>
@@ -893,7 +896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>2146</v>
       </c>
@@ -904,7 +907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>2151</v>
       </c>
@@ -915,7 +918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>2153</v>
       </c>
@@ -926,7 +929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>2162</v>
       </c>
@@ -946,15 +949,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C92C7E-29F0-43F7-83E4-D3D6804A5EBC}">
   <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
@@ -965,7 +968,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -976,7 +979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -987,7 +990,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -998,7 +1001,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1009,7 +1012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1020,7 +1023,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1031,7 +1034,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1042,7 +1045,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1053,7 +1056,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1075,7 +1078,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1086,7 +1089,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1097,7 +1100,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1108,7 +1111,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1119,7 +1122,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1130,7 +1133,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1141,7 +1144,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1152,7 +1155,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1163,7 +1166,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1174,7 +1177,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1185,7 +1188,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1196,7 +1199,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1207,7 +1210,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1218,7 +1221,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1229,7 +1232,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1251,7 +1254,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1262,7 +1265,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1273,7 +1276,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1284,7 +1287,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1296,6 +1299,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C31" xr:uid="{47C92C7E-29F0-43F7-83E4-D3D6804A5EBC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1303,14 +1307,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1F451E-A246-49AD-A713-E24E2BFAE5FA}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" customWidth="1"/>
+    <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
@@ -1321,7 +1325,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>212</v>
       </c>
@@ -1332,7 +1336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>213</v>
       </c>
@@ -1343,7 +1347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>211</v>
       </c>
@@ -1354,7 +1358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>216</v>
       </c>
@@ -1365,7 +1369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>217</v>
       </c>
@@ -1376,7 +1380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>214</v>
       </c>
